--- a/src/main/resources/projectGit.xlsx
+++ b/src/main/resources/projectGit.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5708F167-8758-4073-85FC-19F5CD3D7DD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CEF0386-838D-0246-BEC7-D18FDA72B5BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4440" yWindow="760" windowWidth="23260" windowHeight="12580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,16 +14,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$A$38</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>https://gitlab.hundsun.com/ifms6.0/project/16596.NJYH/lcpt-njyh.git</t>
   </si>
@@ -89,6 +84,37 @@
   </si>
   <si>
     <t>16596.NJYH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11265.WZYH</t>
+  </si>
+  <si>
+    <t>86567.MTSH</t>
+  </si>
+  <si>
+    <t>87200.YBSH</t>
+  </si>
+  <si>
+    <t>91900.ZHNSH</t>
+  </si>
+  <si>
+    <t>https://gitlab.hundsun.com/ifms6.0/project/11265.WZYH/lcpt-wzyh.git</t>
+  </si>
+  <si>
+    <t>https://gitlab.hundsun.com/ifms6.0/project/86567.MTSH/lcpt-mtsh.git</t>
+  </si>
+  <si>
+    <t>https://gitlab.hundsun.com/ifms6.0/project/87200.YBSH/lcpt-ybsh.git</t>
+  </si>
+  <si>
+    <t>https://gitlab.hundsun.com/ifms6.0/project/91900.ZHNSH/lcpt-zhnsh.git</t>
+  </si>
+  <si>
+    <t>https://gitlab.hundsun.com/ifms6.0/project/16874.HUISYH/lcpt-huisyh.git</t>
+  </si>
+  <si>
+    <t>16874.HUISYH</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -96,7 +122,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -105,6 +131,7 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -161,9 +188,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -201,9 +228,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -236,26 +263,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -288,26 +298,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -483,14 +476,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:B45"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="45.59765625" customWidth="1"/>
-    <col min="3" max="3" width="50.59765625" customWidth="1"/>
+    <col min="2" max="2" width="45.6640625" customWidth="1"/>
+    <col min="3" max="3" width="50.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="3" t="s">
         <v>21</v>
       </c>
@@ -498,7 +491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -506,7 +499,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -514,7 +507,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -522,7 +515,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -530,7 +523,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -538,7 +531,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -546,7 +539,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -554,7 +547,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -562,7 +555,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -570,7 +563,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -578,149 +571,161 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2">
       <c r="A38" s="1"/>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2">
       <c r="A39" s="1"/>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2">
       <c r="A40" s="1"/>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2">
       <c r="A41" s="1"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2">
       <c r="A43" s="2"/>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2">
       <c r="A44" s="3"/>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2">
       <c r="A45" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{CC9E54EA-60D3-4AFD-A936-2742782FF752}"/>
-    <hyperlink ref="B3" r:id="rId2" xr:uid="{4BAF8C2B-5F3A-41CE-A031-662622A6305C}"/>
-    <hyperlink ref="B4" r:id="rId3" xr:uid="{6223FC9F-5BE0-4FD7-9759-3ED46C1BA4E6}"/>
-    <hyperlink ref="B5" r:id="rId4" xr:uid="{B7BCEE64-EDB8-4C6D-82E6-844A01DCBA0C}"/>
-    <hyperlink ref="B6" r:id="rId5" xr:uid="{32404214-C206-41F3-A00B-9B80DDDBEEB9}"/>
-    <hyperlink ref="B7" r:id="rId6" xr:uid="{EEEBCED6-B979-40DC-A355-C58F50BB34A7}"/>
-    <hyperlink ref="B8" r:id="rId7" xr:uid="{CB32346F-40AE-42DC-B759-63C07418E833}"/>
-    <hyperlink ref="B9" r:id="rId8" xr:uid="{B3D3376C-CF9F-42BF-8B13-B6B37784CD52}"/>
-    <hyperlink ref="B10" r:id="rId9" xr:uid="{1574993C-535B-42C9-8F8F-F9A5107DB8FD}"/>
-    <hyperlink ref="B11" r:id="rId10" xr:uid="{6B71E86E-9AED-4A47-81D3-CB0FC1855BC9}"/>
-    <hyperlink ref="A1" r:id="rId11" display="https://gitlab.hundsun.com/ifms6.0/project/16596.NJYH/lcpt-njyh.git" xr:uid="{B18B4CC3-F2DF-482E-B79B-DE15816E822A}"/>
-    <hyperlink ref="B1" r:id="rId12" xr:uid="{B9B93F1B-BB10-4A7C-9966-7CEA3F08AD7F}"/>
+    <hyperlink ref="B12" r:id="rId1" xr:uid="{3353B5D4-7D65-F245-93DB-8BEA70EFF3A0}"/>
+    <hyperlink ref="B13" r:id="rId2" xr:uid="{D1F98769-D6AB-D54D-B8C9-4A6AD6E91A61}"/>
+    <hyperlink ref="B14" r:id="rId3" xr:uid="{8BD6700D-83E0-EB40-9038-4F1483A2BEA2}"/>
+    <hyperlink ref="B15" r:id="rId4" xr:uid="{A814DAE1-187B-5142-B613-4F97EEE432B5}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId13"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId5"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>